--- a/Supplementary_database_totalE_2.xlsx
+++ b/Supplementary_database_totalE_2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chanapromcholsuk/Nextcloud3/PhD-Nos/database/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chanapromcholsuk/Documents/GitHub/hBN-database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C8BC383-F09C-444B-9618-0FCA29DD01C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EA45AA1-C8F2-3C4A-9B91-B5818CCB5215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="500" windowWidth="28800" windowHeight="16240" xr2:uid="{F95D7E04-E59A-AB4B-8312-7C399E318179}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" xr2:uid="{F95D7E04-E59A-AB4B-8312-7C399E318179}"/>
   </bookViews>
   <sheets>
     <sheet name="updated_data" sheetId="6" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4487" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4489" uniqueCount="377">
   <si>
     <t>Defect</t>
   </si>
@@ -1165,6 +1165,12 @@
   <si>
     <t>Excited-state total energy (eV)</t>
   </si>
+  <si>
+    <t>Al_B</t>
+  </si>
+  <si>
+    <t>bulk</t>
+  </si>
 </sst>
 </file>
 
@@ -1793,7 +1799,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5622CDE-E4E8-174B-8ADD-69F441A17979}">
-  <dimension ref="A1:AD277"/>
+  <dimension ref="A1:AD278"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -27303,6 +27309,14 @@
         <v>-964.00852999999995</v>
       </c>
     </row>
+    <row r="278" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A278" t="s">
+        <v>375</v>
+      </c>
+      <c r="B278" s="21" t="s">
+        <v>376</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Supplementary_database_totalE_2.xlsx
+++ b/Supplementary_database_totalE_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chanapromcholsuk/Documents/GitHub/hBN-database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EA45AA1-C8F2-3C4A-9B91-B5818CCB5215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1607C006-DB2B-254B-BA62-5B5572746DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" xr2:uid="{F95D7E04-E59A-AB4B-8312-7C399E318179}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4489" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4487" uniqueCount="375">
   <si>
     <t>Defect</t>
   </si>
@@ -1165,12 +1165,6 @@
   <si>
     <t>Excited-state total energy (eV)</t>
   </si>
-  <si>
-    <t>Al_B</t>
-  </si>
-  <si>
-    <t>bulk</t>
-  </si>
 </sst>
 </file>
 
@@ -27310,12 +27304,7 @@
       </c>
     </row>
     <row r="278" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A278" t="s">
-        <v>375</v>
-      </c>
-      <c r="B278" s="21" t="s">
-        <v>376</v>
-      </c>
+      <c r="B278" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary_database_totalE_2.xlsx
+++ b/Supplementary_database_totalE_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chanapromcholsuk/Documents/GitHub/hBN-database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1607C006-DB2B-254B-BA62-5B5572746DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18ED5EA3-B38C-0647-BE2A-884757087949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" xr2:uid="{F95D7E04-E59A-AB4B-8312-7C399E318179}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4487" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4487" uniqueCount="376">
   <si>
     <t>Defect</t>
   </si>
@@ -1165,6 +1165,9 @@
   <si>
     <t>Excited-state total energy (eV)</t>
   </si>
+  <si>
+    <t>AlBNBVN-test</t>
+  </si>
 </sst>
 </file>
 
@@ -1913,7 +1916,7 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="21" t="s">
-        <v>167</v>
+        <v>375</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>11</v>

--- a/Supplementary_database_totalE_2.xlsx
+++ b/Supplementary_database_totalE_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chanapromcholsuk/Documents/GitHub/hBN-database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18ED5EA3-B38C-0647-BE2A-884757087949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{020EE18C-97CE-A642-A8B5-591EDBBA441C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" xr2:uid="{F95D7E04-E59A-AB4B-8312-7C399E318179}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4487" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4487" uniqueCount="375">
   <si>
     <t>Defect</t>
   </si>
@@ -1165,9 +1165,6 @@
   <si>
     <t>Excited-state total energy (eV)</t>
   </si>
-  <si>
-    <t>AlBNBVN-test</t>
-  </si>
 </sst>
 </file>
 
@@ -1916,7 +1913,7 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="21" t="s">
-        <v>375</v>
+        <v>167</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>11</v>

--- a/Supplementary_database_totalE_2.xlsx
+++ b/Supplementary_database_totalE_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chanapromcholsuk/Documents/GitHub/hBN-database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A4A11DE-95AF-F54C-B17D-624E4EC38259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62C098B0-A8AD-9B41-80ED-7C16FAC82849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" xr2:uid="{F95D7E04-E59A-AB4B-8312-7C399E318179}"/>
   </bookViews>
@@ -1925,7 +1925,7 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>167</v>
@@ -2020,7 +2020,7 @@
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B3" s="21" t="s">
         <v>167</v>
@@ -10760,7 +10760,7 @@
     </row>
     <row r="95" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B95" s="21" t="s">
         <v>202</v>

--- a/Supplementary_database_totalE_2.xlsx
+++ b/Supplementary_database_totalE_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chanapromcholsuk/Documents/GitHub/hBN-database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62C098B0-A8AD-9B41-80ED-7C16FAC82849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C29E74D8-B280-E448-AC46-B318C17D9B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" xr2:uid="{F95D7E04-E59A-AB4B-8312-7C399E318179}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5595" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5600" uniqueCount="380">
   <si>
     <t>Defect</t>
   </si>
@@ -1174,6 +1174,12 @@
   <si>
     <t>monolayer</t>
   </si>
+  <si>
+    <t>Al$_B$</t>
+  </si>
+  <si>
+    <t>AlB</t>
+  </si>
 </sst>
 </file>
 
@@ -10760,7 +10766,7 @@
     </row>
     <row r="95" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B95" s="21" t="s">
         <v>202</v>
@@ -28144,7 +28150,75 @@
       </c>
     </row>
     <row r="278" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C278" s="21"/>
+      <c r="A278" t="s">
+        <v>375</v>
+      </c>
+      <c r="B278" t="s">
+        <v>379</v>
+      </c>
+      <c r="C278" t="s">
+        <v>378</v>
+      </c>
+      <c r="D278">
+        <v>0</v>
+      </c>
+      <c r="E278" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="F278" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="G278">
+        <v>7.2227027514807302E-3</v>
+      </c>
+      <c r="H278">
+        <v>8.0883651007363049E-3</v>
+      </c>
+      <c r="I278">
+        <v>1.2164835880351879E-5</v>
+      </c>
+      <c r="J278" s="13">
+        <v>0.99999937076178347</v>
+      </c>
+      <c r="K278">
+        <v>1.0843856925572579E-2</v>
+      </c>
+      <c r="L278">
+        <v>141639.10650260249</v>
+      </c>
+      <c r="M278">
+        <v>11.76396412527289</v>
+      </c>
+      <c r="N278">
+        <v>9.4960979845805146E-3</v>
+      </c>
+      <c r="O278">
+        <v>1.1531719363232339E-3</v>
+      </c>
+      <c r="P278">
+        <v>1.392379467423873E-5</v>
+      </c>
+      <c r="Q278">
+        <v>0.99999894065731854</v>
+      </c>
+      <c r="R278">
+        <v>9.5658703900656991E-3</v>
+      </c>
+      <c r="S278">
+        <v>5.8204999999998108</v>
+      </c>
+      <c r="T278">
+        <v>213.04011682845811</v>
+      </c>
+      <c r="U278">
+        <v>182012.7249690902</v>
+      </c>
+      <c r="V278">
+        <v>6.9238181128376084</v>
+      </c>
+      <c r="W278">
+        <v>4.8401460124352838</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary_database_totalE_2.xlsx
+++ b/Supplementary_database_totalE_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chanapromcholsuk/Documents/GitHub/hBN-database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C29E74D8-B280-E448-AC46-B318C17D9B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B25367-19BB-0749-8730-B2FA1F1B183D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" xr2:uid="{F95D7E04-E59A-AB4B-8312-7C399E318179}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5600" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5615" uniqueCount="380">
   <si>
     <t>Defect</t>
   </si>
@@ -1353,7 +1353,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1486,6 +1486,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="11" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="11" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -28219,6 +28224,30 @@
       <c r="W278">
         <v>4.8401460124352838</v>
       </c>
+      <c r="X278" s="68">
+        <v>0</v>
+      </c>
+      <c r="Y278" s="69">
+        <v>0</v>
+      </c>
+      <c r="Z278" s="68">
+        <v>0</v>
+      </c>
+      <c r="AA278" s="68">
+        <v>0</v>
+      </c>
+      <c r="AB278" s="70">
+        <v>0</v>
+      </c>
+      <c r="AC278" s="60">
+        <v>0</v>
+      </c>
+      <c r="AD278">
+        <v>0</v>
+      </c>
+      <c r="AE278">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -28228,7 +28257,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D8B75AF-C9D8-4226-AF82-E0554200F8F0}">
-  <dimension ref="A1:M277"/>
+  <dimension ref="A1:M278"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11"/>
@@ -39601,6 +39630,47 @@
         <v>1.00825E-4</v>
       </c>
     </row>
+    <row r="278" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A278" t="s">
+        <v>375</v>
+      </c>
+      <c r="B278" t="s">
+        <v>379</v>
+      </c>
+      <c r="C278" t="s">
+        <v>378</v>
+      </c>
+      <c r="D278">
+        <v>0</v>
+      </c>
+      <c r="E278" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="F278" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="G278">
+        <v>7.2227027514807302E-3</v>
+      </c>
+      <c r="H278">
+        <v>8.0883651007363049E-3</v>
+      </c>
+      <c r="I278">
+        <v>1.2164835880351879E-5</v>
+      </c>
+      <c r="J278" s="13">
+        <v>0.99999937076178347</v>
+      </c>
+      <c r="K278">
+        <v>1.0843856925572579E-2</v>
+      </c>
+      <c r="L278">
+        <v>141639.10650260249</v>
+      </c>
+      <c r="M278">
+        <v>11.76396412527289</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -39608,7 +39678,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A562EA6B-BD8E-44CE-8054-D7C74738C5AA}">
-  <dimension ref="A1:S277"/>
+  <dimension ref="A1:S278"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17" customWidth="1"/>
@@ -55969,6 +56039,65 @@
         <v>-964.00852999999995</v>
       </c>
     </row>
+    <row r="278" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A278" t="s">
+        <v>375</v>
+      </c>
+      <c r="B278" t="s">
+        <v>379</v>
+      </c>
+      <c r="C278" t="s">
+        <v>378</v>
+      </c>
+      <c r="D278">
+        <v>0</v>
+      </c>
+      <c r="E278" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="F278" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="G278">
+        <v>9.4960979845805146E-3</v>
+      </c>
+      <c r="H278">
+        <v>1.1531719363232339E-3</v>
+      </c>
+      <c r="I278">
+        <v>1.392379467423873E-5</v>
+      </c>
+      <c r="J278">
+        <v>0.99999894065731854</v>
+      </c>
+      <c r="K278">
+        <v>9.5658703900656991E-3</v>
+      </c>
+      <c r="L278">
+        <v>5.8204999999998108</v>
+      </c>
+      <c r="M278">
+        <v>213.04011682845811</v>
+      </c>
+      <c r="N278">
+        <v>182012.7249690902</v>
+      </c>
+      <c r="O278">
+        <v>6.9238181128376084</v>
+      </c>
+      <c r="P278">
+        <v>4.8401460124352838</v>
+      </c>
+      <c r="Q278">
+        <v>5.1863551840125373E-2</v>
+      </c>
+      <c r="R278">
+        <v>0</v>
+      </c>
+      <c r="S278">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -55977,7 +56106,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571C821E-6F69-447B-A9F4-4FC351CC5CA1}">
-  <dimension ref="A1:L277"/>
+  <dimension ref="A1:L278"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17" customWidth="1"/>
@@ -65691,6 +65820,41 @@
         <v>97.713978589800504</v>
       </c>
     </row>
+    <row r="278" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A278" t="s">
+        <v>375</v>
+      </c>
+      <c r="B278" t="s">
+        <v>379</v>
+      </c>
+      <c r="C278" t="s">
+        <v>378</v>
+      </c>
+      <c r="D278">
+        <v>0</v>
+      </c>
+      <c r="E278" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="F278" s="43" t="s">
+        <v>12</v>
+      </c>
+      <c r="G278" s="68">
+        <v>0</v>
+      </c>
+      <c r="H278" s="69">
+        <v>0</v>
+      </c>
+      <c r="I278" s="68">
+        <v>0</v>
+      </c>
+      <c r="J278" s="68">
+        <v>0</v>
+      </c>
+      <c r="K278" s="70">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>

--- a/Supplementary_database_totalE_2.xlsx
+++ b/Supplementary_database_totalE_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chanapromcholsuk/Documents/GitHub/hBN-database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B25367-19BB-0749-8730-B2FA1F1B183D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C165D2-56E4-424D-A93B-1EF884EDA510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" xr2:uid="{F95D7E04-E59A-AB4B-8312-7C399E318179}"/>
   </bookViews>
@@ -1353,7 +1353,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1490,6 +1490,24 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="11" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -28156,7 +28174,7 @@
     </row>
     <row r="278" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B278" t="s">
         <v>379</v>
@@ -28164,7 +28182,7 @@
       <c r="C278" t="s">
         <v>378</v>
       </c>
-      <c r="D278">
+      <c r="D278" s="71">
         <v>0</v>
       </c>
       <c r="E278" s="1" t="s">
@@ -28173,73 +28191,73 @@
       <c r="F278" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="G278">
+      <c r="G278" s="71">
         <v>7.2227027514807302E-3</v>
       </c>
-      <c r="H278">
+      <c r="H278" s="71">
         <v>8.0883651007363049E-3</v>
       </c>
-      <c r="I278">
+      <c r="I278" s="71">
         <v>1.2164835880351879E-5</v>
       </c>
-      <c r="J278" s="13">
+      <c r="J278" s="72">
         <v>0.99999937076178347</v>
       </c>
-      <c r="K278">
+      <c r="K278" s="71">
         <v>1.0843856925572579E-2</v>
       </c>
-      <c r="L278">
+      <c r="L278" s="71">
         <v>141639.10650260249</v>
       </c>
-      <c r="M278">
+      <c r="M278" s="71">
         <v>11.76396412527289</v>
       </c>
-      <c r="N278">
+      <c r="N278" s="71">
         <v>9.4960979845805146E-3</v>
       </c>
-      <c r="O278">
+      <c r="O278" s="71">
         <v>1.1531719363232339E-3</v>
       </c>
-      <c r="P278">
+      <c r="P278" s="71">
         <v>1.392379467423873E-5</v>
       </c>
-      <c r="Q278">
+      <c r="Q278" s="71">
         <v>0.99999894065731854</v>
       </c>
-      <c r="R278">
+      <c r="R278" s="71">
         <v>9.5658703900656991E-3</v>
       </c>
-      <c r="S278">
+      <c r="S278" s="71">
         <v>5.8204999999998108</v>
       </c>
-      <c r="T278">
+      <c r="T278" s="71">
         <v>213.04011682845811</v>
       </c>
-      <c r="U278">
+      <c r="U278" s="71">
         <v>182012.7249690902</v>
       </c>
-      <c r="V278">
+      <c r="V278" s="73">
         <v>6.9238181128376084</v>
       </c>
-      <c r="W278">
+      <c r="W278" s="73">
         <v>4.8401460124352838</v>
       </c>
-      <c r="X278" s="68">
-        <v>0</v>
-      </c>
-      <c r="Y278" s="69">
-        <v>0</v>
-      </c>
-      <c r="Z278" s="68">
-        <v>0</v>
-      </c>
-      <c r="AA278" s="68">
-        <v>0</v>
-      </c>
-      <c r="AB278" s="70">
-        <v>0</v>
-      </c>
-      <c r="AC278" s="60">
+      <c r="X278" s="74">
+        <v>0</v>
+      </c>
+      <c r="Y278" s="75">
+        <v>0</v>
+      </c>
+      <c r="Z278" s="74">
+        <v>0</v>
+      </c>
+      <c r="AA278" s="74">
+        <v>0</v>
+      </c>
+      <c r="AB278" s="75">
+        <v>0</v>
+      </c>
+      <c r="AC278" s="76">
         <v>0</v>
       </c>
       <c r="AD278">

--- a/Supplementary_database_totalE_2.xlsx
+++ b/Supplementary_database_totalE_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chanapromcholsuk/Documents/GitHub/hBN-database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13B53961-E1C8-BB43-BB2C-32D5F2DDF8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAF4AADD-7FCF-2143-A8A2-3F82A513AA80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" activeTab="3" xr2:uid="{F95D7E04-E59A-AB4B-8312-7C399E318179}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" xr2:uid="{F95D7E04-E59A-AB4B-8312-7C399E318179}"/>
   </bookViews>
   <sheets>
     <sheet name="updated_data" sheetId="6" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5615" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5610" uniqueCount="379">
   <si>
     <t>Defect</t>
   </si>
@@ -1350,7 +1350,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1487,24 +1487,6 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="11" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -1828,7 +1810,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5622CDE-E4E8-174B-8ADD-69F441A17979}">
-  <dimension ref="A1:AE278"/>
+  <dimension ref="A1:AE277"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17" customWidth="1"/>
@@ -28169,101 +28151,6 @@
         <v>-964.00852999999995</v>
       </c>
     </row>
-    <row r="278" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A278" t="s">
-        <v>376</v>
-      </c>
-      <c r="B278" t="s">
-        <v>378</v>
-      </c>
-      <c r="C278" t="s">
-        <v>377</v>
-      </c>
-      <c r="D278" s="71">
-        <v>0</v>
-      </c>
-      <c r="E278" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="F278" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="G278" s="71">
-        <v>7.2227027514807302E-3</v>
-      </c>
-      <c r="H278" s="71">
-        <v>8.0883651007363049E-3</v>
-      </c>
-      <c r="I278" s="71">
-        <v>1.2164835880351879E-5</v>
-      </c>
-      <c r="J278" s="72">
-        <v>0.99999937076178347</v>
-      </c>
-      <c r="K278" s="71">
-        <v>1.0843856925572579E-2</v>
-      </c>
-      <c r="L278" s="71">
-        <v>141639.10650260249</v>
-      </c>
-      <c r="M278" s="71">
-        <v>11.76396412527289</v>
-      </c>
-      <c r="N278" s="71">
-        <v>9.4960979845805146E-3</v>
-      </c>
-      <c r="O278" s="71">
-        <v>1.1531719363232339E-3</v>
-      </c>
-      <c r="P278" s="71">
-        <v>1.392379467423873E-5</v>
-      </c>
-      <c r="Q278" s="71">
-        <v>0.99999894065731854</v>
-      </c>
-      <c r="R278" s="71">
-        <v>9.5658703900656991E-3</v>
-      </c>
-      <c r="S278" s="71">
-        <v>5.8204999999998108</v>
-      </c>
-      <c r="T278" s="71">
-        <v>213.04011682845811</v>
-      </c>
-      <c r="U278" s="71">
-        <v>182012.7249690902</v>
-      </c>
-      <c r="V278" s="73">
-        <v>6.9238181128376084</v>
-      </c>
-      <c r="W278" s="73">
-        <v>4.8401460124352838</v>
-      </c>
-      <c r="X278" s="74">
-        <v>0</v>
-      </c>
-      <c r="Y278" s="75">
-        <v>0</v>
-      </c>
-      <c r="Z278" s="74">
-        <v>0</v>
-      </c>
-      <c r="AA278" s="74">
-        <v>0</v>
-      </c>
-      <c r="AB278" s="75">
-        <v>0</v>
-      </c>
-      <c r="AC278" s="76">
-        <v>0</v>
-      </c>
-      <c r="AD278">
-        <v>0</v>
-      </c>
-      <c r="AE278">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Supplementary_database_totalE_2.xlsx
+++ b/Supplementary_database_totalE_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chanapromcholsuk/Documents/GitHub/hBN-database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAF4AADD-7FCF-2143-A8A2-3F82A513AA80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9720F318-0498-814D-B1F2-3C2FFDFB407F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" xr2:uid="{F95D7E04-E59A-AB4B-8312-7C399E318179}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" activeTab="3" xr2:uid="{F95D7E04-E59A-AB4B-8312-7C399E318179}"/>
   </bookViews>
   <sheets>
     <sheet name="updated_data" sheetId="6" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5610" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5595" uniqueCount="377">
   <si>
     <t>Defect</t>
   </si>
@@ -1171,12 +1171,6 @@
   <si>
     <t>monolayer</t>
   </si>
-  <si>
-    <t>Al$_B$</t>
-  </si>
-  <si>
-    <t>AlB</t>
-  </si>
 </sst>
 </file>
 
@@ -1350,7 +1344,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1483,11 +1477,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="11" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="11" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -28159,7 +28148,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D8B75AF-C9D8-4226-AF82-E0554200F8F0}">
-  <dimension ref="A1:M278"/>
+  <dimension ref="A1:M277"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11"/>
@@ -39532,47 +39521,6 @@
         <v>1.00825E-4</v>
       </c>
     </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A278" t="s">
-        <v>376</v>
-      </c>
-      <c r="B278" t="s">
-        <v>378</v>
-      </c>
-      <c r="C278" t="s">
-        <v>377</v>
-      </c>
-      <c r="D278">
-        <v>0</v>
-      </c>
-      <c r="E278" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="F278" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="G278">
-        <v>7.2227027514807302E-3</v>
-      </c>
-      <c r="H278">
-        <v>8.0883651007363049E-3</v>
-      </c>
-      <c r="I278">
-        <v>1.2164835880351879E-5</v>
-      </c>
-      <c r="J278" s="13">
-        <v>0.99999937076178347</v>
-      </c>
-      <c r="K278">
-        <v>1.0843856925572579E-2</v>
-      </c>
-      <c r="L278">
-        <v>141639.10650260249</v>
-      </c>
-      <c r="M278">
-        <v>11.76396412527289</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -39580,7 +39528,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A562EA6B-BD8E-44CE-8054-D7C74738C5AA}">
-  <dimension ref="A1:S278"/>
+  <dimension ref="A1:S277"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17" customWidth="1"/>
@@ -55941,65 +55889,6 @@
         <v>-964.00852999999995</v>
       </c>
     </row>
-    <row r="278" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A278" t="s">
-        <v>376</v>
-      </c>
-      <c r="B278" t="s">
-        <v>378</v>
-      </c>
-      <c r="C278" t="s">
-        <v>377</v>
-      </c>
-      <c r="D278">
-        <v>0</v>
-      </c>
-      <c r="E278" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="F278" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="G278">
-        <v>9.4960979845805146E-3</v>
-      </c>
-      <c r="H278">
-        <v>1.1531719363232339E-3</v>
-      </c>
-      <c r="I278">
-        <v>1.392379467423873E-5</v>
-      </c>
-      <c r="J278">
-        <v>0.99999894065731854</v>
-      </c>
-      <c r="K278">
-        <v>9.5658703900656991E-3</v>
-      </c>
-      <c r="L278">
-        <v>5.8204999999998108</v>
-      </c>
-      <c r="M278">
-        <v>213.04011682845811</v>
-      </c>
-      <c r="N278">
-        <v>182012.7249690902</v>
-      </c>
-      <c r="O278">
-        <v>6.9238181128376084</v>
-      </c>
-      <c r="P278">
-        <v>4.8401460124352838</v>
-      </c>
-      <c r="Q278">
-        <v>5.1863551840125373E-2</v>
-      </c>
-      <c r="R278">
-        <v>0</v>
-      </c>
-      <c r="S278">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -56008,7 +55897,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571C821E-6F69-447B-A9F4-4FC351CC5CA1}">
-  <dimension ref="A1:L278"/>
+  <dimension ref="A1:L277"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17" customWidth="1"/>
@@ -65722,41 +65611,6 @@
         <v>97.713978589800504</v>
       </c>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A278" t="s">
-        <v>376</v>
-      </c>
-      <c r="B278" t="s">
-        <v>378</v>
-      </c>
-      <c r="C278" t="s">
-        <v>377</v>
-      </c>
-      <c r="D278">
-        <v>0</v>
-      </c>
-      <c r="E278" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="F278" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="G278" s="68">
-        <v>0</v>
-      </c>
-      <c r="H278" s="69">
-        <v>0</v>
-      </c>
-      <c r="I278" s="68">
-        <v>0</v>
-      </c>
-      <c r="J278" s="68">
-        <v>0</v>
-      </c>
-      <c r="K278" s="70">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>

--- a/Supplementary_database_totalE_2.xlsx
+++ b/Supplementary_database_totalE_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chanapromcholsuk/Documents/GitHub/hBN-database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E283AC4-1CD2-5343-A47B-A5CA3BD421FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B093C34E-8AB3-6841-8786-70FFD4E7F270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" activeTab="3" xr2:uid="{F95D7E04-E59A-AB4B-8312-7C399E318179}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" xr2:uid="{F95D7E04-E59A-AB4B-8312-7C399E318179}"/>
   </bookViews>
   <sheets>
     <sheet name="updated_data" sheetId="6" r:id="rId1"/>
@@ -28186,7 +28186,7 @@
         <v>0</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F278" s="43" t="s">
         <v>12</v>

--- a/Supplementary_database_totalE_2.xlsx
+++ b/Supplementary_database_totalE_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chanapromcholsuk/Documents/GitHub/hBN-database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B093C34E-8AB3-6841-8786-70FFD4E7F270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEAC1111-6246-9843-8F4A-886CFFBFD897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" xr2:uid="{F95D7E04-E59A-AB4B-8312-7C399E318179}"/>
   </bookViews>
@@ -28186,7 +28186,7 @@
         <v>0</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F278" s="43" t="s">
         <v>12</v>

--- a/Supplementary_database_totalE_2.xlsx
+++ b/Supplementary_database_totalE_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chanapromcholsuk/Documents/GitHub/hBN-database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEAC1111-6246-9843-8F4A-886CFFBFD897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F6E53F7-D97F-AE4A-BB03-4DC3161BB376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16120" xr2:uid="{F95D7E04-E59A-AB4B-8312-7C399E318179}"/>
   </bookViews>
@@ -28186,7 +28186,7 @@
         <v>0</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F278" s="43" t="s">
         <v>12</v>
